--- a/public/descargas/listas-dependientes/listas-desplegables-dependientes.xlsx
+++ b/public/descargas/listas-dependientes/listas-desplegables-dependientes.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\edwinortizNET\public\descargas\listas-dependientes\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{0EE0F71F-72D8-4863-8855-62E910A23334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
